--- a/output/audit_torino.xlsx
+++ b/output/audit_torino.xlsx
@@ -64,12 +64,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,16 +434,16 @@
   <dimension ref="A1:J201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" style="4" min="1" max="1"/>
+    <col width="7" customWidth="1" style="4" min="2" max="2"/>
+    <col width="8" customWidth="1" style="4" min="3" max="3"/>
+    <col width="11" customWidth="1" style="4" min="4" max="4"/>
+    <col width="20" customWidth="1" style="4" min="5" max="5"/>
+    <col width="15" customWidth="1" style="4" min="6" max="6"/>
+    <col width="18" customWidth="1" style="4" min="7" max="7"/>
+    <col width="17" customWidth="1" style="4" min="8" max="8"/>
+    <col width="22" customWidth="1" style="4" min="9" max="9"/>
+    <col width="30" customWidth="1" style="4" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -534,9 +530,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -570,9 +569,12 @@
           <t>12,89</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -606,9 +608,12 @@
           <t>479,50</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -642,9 +647,12 @@
           <t>195</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -678,9 +686,12 @@
           <t>541,92</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -714,9 +725,12 @@
           <t>152</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -750,9 +764,12 @@
           <t>509,02</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -786,9 +803,12 @@
           <t>62</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -822,9 +842,12 @@
           <t>960,45</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -858,9 +881,12 @@
           <t>47</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -894,9 +920,12 @@
           <t>2.494,13</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -930,9 +959,12 @@
           <t>6.230,14</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -966,9 +998,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1002,9 +1037,12 @@
           <t>23,67</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1038,9 +1076,12 @@
           <t>32,18</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1074,9 +1115,12 @@
           <t>508,68</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1110,9 +1154,12 @@
           <t>693,45</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1146,9 +1193,12 @@
           <t>156</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1182,9 +1232,12 @@
           <t>13</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1218,9 +1271,12 @@
           <t>853,51</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1254,9 +1310,12 @@
           <t>2.683,99</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1290,9 +1349,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1326,9 +1388,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1362,9 +1427,12 @@
           <t>24.236,82</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1398,9 +1466,12 @@
           <t>60</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1434,9 +1505,12 @@
           <t>34,55</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1470,9 +1544,12 @@
           <t>342</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1506,9 +1583,12 @@
           <t>149</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1542,9 +1622,12 @@
           <t>508</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1578,9 +1661,12 @@
           <t>1.821,71</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1614,9 +1700,12 @@
           <t>112</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1650,9 +1739,12 @@
           <t>34</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1686,9 +1778,12 @@
           <t>894,77</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1722,9 +1817,12 @@
           <t>1.878,26</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1758,9 +1856,12 @@
           <t>891,47</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1794,9 +1895,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1830,9 +1934,12 @@
           <t>162</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1866,9 +1973,12 @@
           <t>470</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1902,9 +2012,12 @@
           <t>76,54</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1938,9 +2051,12 @@
           <t>674</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1974,9 +2090,12 @@
           <t>765</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2010,9 +2129,12 @@
           <t>661,74</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2046,9 +2168,12 @@
           <t>1.351,32</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2082,9 +2207,12 @@
           <t>403</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2118,9 +2246,12 @@
           <t>1.291,76</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2154,9 +2285,12 @@
           <t>1.508,64</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2190,9 +2324,12 @@
           <t>685,70</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2226,9 +2363,12 @@
           <t>6.711,85</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2262,9 +2402,12 @@
           <t>0,23</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2298,9 +2441,12 @@
           <t>8</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2334,9 +2480,12 @@
           <t>65,59</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2370,9 +2519,12 @@
           <t>122,30</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2406,9 +2558,12 @@
           <t>159,56</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2442,9 +2597,12 @@
           <t>206,01</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2478,9 +2636,12 @@
           <t>971,64</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2514,9 +2675,12 @@
           <t>159,00</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2550,9 +2714,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2586,9 +2753,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2622,9 +2792,12 @@
           <t>234,53</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2658,9 +2831,12 @@
           <t>1.065</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2694,9 +2870,12 @@
           <t>21,90</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2730,9 +2909,12 @@
           <t>43,47</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2766,9 +2948,12 @@
           <t>311</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2802,9 +2987,12 @@
           <t>62</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2838,9 +3026,12 @@
           <t>66</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2874,9 +3065,12 @@
           <t>1.117,09</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2910,9 +3104,12 @@
           <t>489,51</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2946,9 +3143,12 @@
           <t>582,38</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2982,9 +3182,12 @@
           <t>3.943,29</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3018,9 +3221,12 @@
           <t>7</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3054,9 +3260,12 @@
           <t>16.967,21</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3090,9 +3299,12 @@
           <t>51.291,55</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3126,9 +3338,12 @@
           <t>21,77</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3162,9 +3377,12 @@
           <t>104</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3198,9 +3416,12 @@
           <t>64</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3234,9 +3455,12 @@
           <t>340,40</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3270,9 +3494,12 @@
           <t>51</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3306,9 +3533,12 @@
           <t>32</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3342,9 +3572,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3378,9 +3611,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3414,9 +3650,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3450,9 +3689,12 @@
           <t>334,00</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3486,9 +3728,12 @@
           <t>18.754,36</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3522,9 +3767,12 @@
           <t>643</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3558,9 +3806,12 @@
           <t>1.092</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3594,9 +3845,12 @@
           <t>1.944,21</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3630,9 +3884,12 @@
           <t>643</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3666,9 +3923,12 @@
           <t>6.107,93</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3702,9 +3962,12 @@
           <t>1.030,34</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -3738,9 +4001,12 @@
           <t>46</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -3774,9 +4040,12 @@
           <t>49</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3810,9 +4079,12 @@
           <t>836,39</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -3846,9 +4118,12 @@
           <t>14</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -3882,9 +4157,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -3918,9 +4196,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -3954,9 +4235,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3990,9 +4274,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4026,9 +4313,12 @@
           <t>256,37</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4062,9 +4352,12 @@
           <t>666</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4098,9 +4391,12 @@
           <t>761</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4134,9 +4430,12 @@
           <t>1.331,85</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4170,9 +4469,12 @@
           <t>416</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4206,9 +4508,12 @@
           <t>1.150,57</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -4242,9 +4547,12 @@
           <t>64</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -4278,9 +4586,12 @@
           <t>19</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -4314,9 +4625,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -4350,9 +4664,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -4386,9 +4703,12 @@
           <t>194</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -4422,9 +4742,12 @@
           <t>393</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -4458,9 +4781,12 @@
           <t>262</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -4494,9 +4820,12 @@
           <t>456</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -4530,9 +4859,12 @@
           <t>517,97</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -4566,9 +4898,12 @@
           <t>431,53</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -4602,9 +4937,12 @@
           <t>238</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -4638,9 +4976,12 @@
           <t>1.456,98</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -4674,9 +5015,12 @@
           <t>33</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -4710,9 +5054,12 @@
           <t>169,65</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -4746,9 +5093,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -4782,9 +5132,12 @@
           <t>4.831</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -4818,9 +5171,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -4854,9 +5210,12 @@
           <t>69,10</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -4890,9 +5249,12 @@
           <t>758,56</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -4926,9 +5288,12 @@
           <t>784,15</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -4962,9 +5327,12 @@
           <t>4.325,01</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -4998,9 +5366,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -5034,9 +5405,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -5070,9 +5444,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -5106,9 +5483,12 @@
           <t>163,06</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -5142,9 +5522,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -5178,9 +5561,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -5214,9 +5600,12 @@
           <t>149</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -5250,9 +5639,12 @@
           <t>198,92</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -5286,9 +5678,12 @@
           <t>538</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -5322,9 +5717,12 @@
           <t>663,21</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -5358,9 +5756,12 @@
           <t>1.266,05</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -5394,9 +5795,12 @@
           <t>321</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -5430,9 +5834,12 @@
           <t>449,83</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -5466,9 +5873,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -5502,9 +5912,12 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -5538,9 +5951,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -5574,9 +5990,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -5610,9 +6029,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -5646,9 +6068,12 @@
           <t>241</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -5682,9 +6107,12 @@
           <t>170</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -5718,9 +6146,12 @@
           <t>446,25</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -5754,9 +6185,12 @@
           <t>711,66</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -5790,9 +6224,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -5826,9 +6263,12 @@
           <t>107,24</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -5862,9 +6302,12 @@
           <t>365,49</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -5898,9 +6341,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -5934,9 +6380,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -5970,9 +6419,12 @@
           <t>209,56</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -6006,9 +6458,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -6042,9 +6497,12 @@
           <t>12,03</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -6078,9 +6536,12 @@
           <t>84,82</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -6114,9 +6575,12 @@
           <t>545</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -6150,9 +6614,12 @@
           <t>116</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -6186,9 +6653,12 @@
           <t>152</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -6222,9 +6692,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -6258,9 +6731,12 @@
           <t>891,48</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -6294,9 +6770,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -6330,9 +6809,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -6366,9 +6848,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -6402,9 +6887,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I165" s="2" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -6438,9 +6926,12 @@
           <t>9.846</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -6474,9 +6965,12 @@
           <t>48</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I167" s="2" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -6510,9 +7004,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -6546,9 +7043,12 @@
           <t>86,83</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I169" s="2" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -6582,9 +7082,12 @@
           <t>622,80</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I170" s="2" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -6618,9 +7121,12 @@
           <t>483,83</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I171" s="2" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -6654,9 +7160,12 @@
           <t>148</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -6690,9 +7199,12 @@
           <t>1.374,60</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I173" s="2" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -6726,9 +7238,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I174" s="2" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -6762,9 +7277,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -6798,9 +7316,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -6834,9 +7355,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -6870,9 +7394,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -6906,9 +7433,12 @@
           <t>162</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -6942,9 +7472,12 @@
           <t>230</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -6978,9 +7511,12 @@
           <t>227</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -7014,9 +7550,12 @@
           <t>748</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -7050,9 +7589,12 @@
           <t>4.598,75</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -7086,9 +7628,12 @@
           <t>280</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -7122,9 +7667,12 @@
           <t>2.535,34</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -7158,9 +7706,12 @@
           <t>924,23</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -7194,9 +7745,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I187" s="2" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -7230,9 +7784,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I188" s="2" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -7266,9 +7823,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I189" s="2" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -7302,9 +7862,12 @@
           <t>14,43</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I190" s="2" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -7338,9 +7901,12 @@
           <t>24,44</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I191" s="2" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -7374,9 +7940,12 @@
           <t>148</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I192" s="2" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -7410,9 +7979,12 @@
           <t>157</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I193" s="2" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -7446,9 +8018,12 @@
           <t>111</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I194" s="2" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -7482,9 +8057,12 @@
           <t>358,80</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I195" s="2" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -7518,9 +8096,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="H196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I196" s="2" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -7554,9 +8135,12 @@
           <t>14</t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I197" s="2" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -7590,9 +8174,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I198" s="2" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -7626,9 +8213,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I199" s="2" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -7662,9 +8252,12 @@
           <t>354,17</t>
         </is>
       </c>
-      <c r="H200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I200" s="2" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -7698,9 +8291,12 @@
           <t>3.662</t>
         </is>
       </c>
-      <c r="H201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I201" s="2" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -7721,7 +8317,7 @@
   <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" style="4" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7731,49 +8327,45 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>1. Aprire il PDF della provincia alla 'pagina PDF' indicata (numero di pagina del file, non quello stampato).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2. Trovare il blocco 'REGIONE AGRARIA n' (colonna 'id': TO1 = regione agraria 1) e la riga della 'classe'.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>3. Guardare solo le colonne TOTALE (Aziende o Superficie, come indicato).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>4. Confrontare con 'valore trascritto': scrivere si se identico, no se diverso.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>5. Se no, scrivere nella colonna successiva il valore come stampato (es. 1.451,79 oppure —).</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Il trattino — significa zero/nessuna azienda.</t>
         </is>

--- a/output/audit_torino.xlsx
+++ b/output/audit_torino.xlsx
@@ -64,8 +64,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,16 +438,16 @@
   <dimension ref="A1:J201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" style="4" min="1" max="1"/>
-    <col width="7" customWidth="1" style="4" min="2" max="2"/>
-    <col width="8" customWidth="1" style="4" min="3" max="3"/>
-    <col width="11" customWidth="1" style="4" min="4" max="4"/>
-    <col width="20" customWidth="1" style="4" min="5" max="5"/>
-    <col width="15" customWidth="1" style="4" min="6" max="6"/>
-    <col width="18" customWidth="1" style="4" min="7" max="7"/>
-    <col width="17" customWidth="1" style="4" min="8" max="8"/>
-    <col width="22" customWidth="1" style="4" min="9" max="9"/>
-    <col width="30" customWidth="1" style="4" min="10" max="10"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,12 +534,9 @@
           <t>31</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -569,12 +570,9 @@
           <t>12,89</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -608,12 +606,9 @@
           <t>479,50</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -647,12 +642,9 @@
           <t>195</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -686,12 +678,9 @@
           <t>541,92</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -725,12 +714,9 @@
           <t>152</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -764,12 +750,9 @@
           <t>509,02</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -803,12 +786,9 @@
           <t>62</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -842,12 +822,9 @@
           <t>960,45</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -881,12 +858,9 @@
           <t>47</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -920,12 +894,9 @@
           <t>2.494,13</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -959,12 +930,9 @@
           <t>6.230,14</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -998,12 +966,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1037,12 +1002,9 @@
           <t>23,67</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1076,12 +1038,9 @@
           <t>32,18</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1115,12 +1074,9 @@
           <t>508,68</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1154,12 +1110,9 @@
           <t>693,45</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1193,12 +1146,9 @@
           <t>156</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1232,12 +1182,9 @@
           <t>13</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1271,12 +1218,9 @@
           <t>853,51</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1310,12 +1254,9 @@
           <t>2.683,99</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1349,12 +1290,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1388,12 +1326,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1427,12 +1362,9 @@
           <t>24.236,82</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1466,12 +1398,9 @@
           <t>60</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1505,12 +1434,9 @@
           <t>34,55</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1544,12 +1470,9 @@
           <t>342</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1583,12 +1506,9 @@
           <t>149</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1622,12 +1542,9 @@
           <t>508</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1661,12 +1578,9 @@
           <t>1.821,71</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1700,12 +1614,9 @@
           <t>112</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1739,12 +1650,9 @@
           <t>34</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1778,12 +1686,9 @@
           <t>894,77</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1817,12 +1722,9 @@
           <t>1.878,26</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1856,12 +1758,9 @@
           <t>891,47</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1895,12 +1794,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1934,12 +1830,9 @@
           <t>162</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1973,12 +1866,9 @@
           <t>470</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2012,12 +1902,9 @@
           <t>76,54</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2051,12 +1938,9 @@
           <t>674</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2090,12 +1974,9 @@
           <t>765</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2129,12 +2010,9 @@
           <t>661,74</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2168,12 +2046,9 @@
           <t>1.351,32</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2207,12 +2082,9 @@
           <t>403</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2246,12 +2118,9 @@
           <t>1.291,76</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2285,12 +2154,9 @@
           <t>1.508,64</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2324,12 +2190,9 @@
           <t>685,70</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2363,12 +2226,9 @@
           <t>6.711,85</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2402,12 +2262,9 @@
           <t>0,23</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2441,12 +2298,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2480,12 +2334,9 @@
           <t>65,59</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2519,12 +2370,9 @@
           <t>122,30</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2558,12 +2406,9 @@
           <t>159,56</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2597,12 +2442,9 @@
           <t>206,01</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2636,12 +2478,9 @@
           <t>971,64</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2675,12 +2514,9 @@
           <t>159,00</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2714,12 +2550,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2753,12 +2586,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2792,12 +2622,9 @@
           <t>234,53</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2831,12 +2658,9 @@
           <t>1.065</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2870,12 +2694,9 @@
           <t>21,90</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2909,12 +2730,9 @@
           <t>43,47</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2948,12 +2766,9 @@
           <t>311</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2987,12 +2802,9 @@
           <t>62</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3026,12 +2838,9 @@
           <t>66</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3065,12 +2874,9 @@
           <t>1.117,09</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3104,12 +2910,9 @@
           <t>489,51</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3143,12 +2946,9 @@
           <t>582,38</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3182,12 +2982,9 @@
           <t>3.943,29</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3221,12 +3018,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3260,12 +3054,9 @@
           <t>16.967,21</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3299,12 +3090,9 @@
           <t>51.291,55</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3338,12 +3126,9 @@
           <t>21,77</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3377,12 +3162,9 @@
           <t>104</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3416,12 +3198,9 @@
           <t>64</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3455,12 +3234,9 @@
           <t>340,40</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3494,12 +3270,9 @@
           <t>51</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3533,12 +3306,9 @@
           <t>32</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3572,12 +3342,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3611,12 +3378,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3650,12 +3414,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3689,12 +3450,9 @@
           <t>334,00</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3728,12 +3486,9 @@
           <t>18.754,36</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3767,12 +3522,9 @@
           <t>643</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3806,12 +3558,9 @@
           <t>1.092</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3845,12 +3594,9 @@
           <t>1.944,21</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3884,12 +3630,9 @@
           <t>643</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3923,12 +3666,9 @@
           <t>6.107,93</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3962,12 +3702,9 @@
           <t>1.030,34</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4001,12 +3738,9 @@
           <t>46</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4040,12 +3774,9 @@
           <t>49</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4079,12 +3810,9 @@
           <t>836,39</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4118,12 +3846,9 @@
           <t>14</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4157,12 +3882,9 @@
           <t>15</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4196,12 +3918,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4235,12 +3954,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4274,12 +3990,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4313,12 +4026,9 @@
           <t>256,37</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4352,12 +4062,9 @@
           <t>666</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4391,12 +4098,9 @@
           <t>761</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4430,12 +4134,9 @@
           <t>1.331,85</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4469,12 +4170,9 @@
           <t>416</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4508,12 +4206,9 @@
           <t>1.150,57</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -4547,12 +4242,9 @@
           <t>64</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -4586,12 +4278,9 @@
           <t>19</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -4625,12 +4314,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H107" s="2" t="inlineStr"/>
       <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -4664,12 +4350,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -4703,12 +4386,9 @@
           <t>194</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H109" s="2" t="inlineStr"/>
       <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -4742,12 +4422,9 @@
           <t>393</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H110" s="2" t="inlineStr"/>
       <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -4781,12 +4458,9 @@
           <t>262</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -4820,12 +4494,9 @@
           <t>456</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -4859,12 +4530,9 @@
           <t>517,97</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -4898,12 +4566,9 @@
           <t>431,53</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -4937,12 +4602,9 @@
           <t>238</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H115" s="2" t="inlineStr"/>
       <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -4976,12 +4638,9 @@
           <t>1.456,98</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5015,12 +4674,9 @@
           <t>33</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H117" s="2" t="inlineStr"/>
       <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5054,12 +4710,9 @@
           <t>169,65</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H118" s="2" t="inlineStr"/>
       <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5093,12 +4746,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H119" s="2" t="inlineStr"/>
       <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5132,12 +4782,9 @@
           <t>4.831</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H120" s="2" t="inlineStr"/>
       <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5171,12 +4818,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H121" s="2" t="inlineStr"/>
       <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5210,12 +4854,9 @@
           <t>69,10</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H122" s="2" t="inlineStr"/>
       <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5249,12 +4890,9 @@
           <t>758,56</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H123" s="2" t="inlineStr"/>
       <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -5288,12 +4926,9 @@
           <t>784,15</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H124" s="2" t="inlineStr"/>
       <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -5327,12 +4962,9 @@
           <t>4.325,01</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H125" s="2" t="inlineStr"/>
       <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -5366,12 +4998,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H126" s="2" t="inlineStr"/>
       <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -5405,12 +5034,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H127" s="2" t="inlineStr"/>
       <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -5444,12 +5070,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H128" s="2" t="inlineStr"/>
       <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -5483,12 +5106,9 @@
           <t>163,06</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H129" s="2" t="inlineStr"/>
       <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -5522,12 +5142,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H130" s="2" t="inlineStr"/>
       <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -5561,12 +5178,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H131" s="2" t="inlineStr"/>
       <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -5600,12 +5214,9 @@
           <t>149</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H132" s="2" t="inlineStr"/>
       <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -5639,12 +5250,9 @@
           <t>198,92</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H133" s="2" t="inlineStr"/>
       <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -5678,12 +5286,9 @@
           <t>538</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H134" s="2" t="inlineStr"/>
       <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -5717,12 +5322,9 @@
           <t>663,21</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H135" s="2" t="inlineStr"/>
       <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -5756,12 +5358,9 @@
           <t>1.266,05</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H136" s="2" t="inlineStr"/>
       <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -5795,12 +5394,9 @@
           <t>321</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H137" s="2" t="inlineStr"/>
       <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -5834,12 +5430,9 @@
           <t>449,83</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H138" s="2" t="inlineStr"/>
       <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -5873,12 +5466,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H139" s="2" t="inlineStr"/>
       <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -5912,12 +5502,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H140" s="2" t="inlineStr"/>
       <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -5951,12 +5538,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H141" s="2" t="inlineStr"/>
       <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -5990,12 +5574,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H142" s="2" t="inlineStr"/>
       <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -6029,12 +5610,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H143" s="2" t="inlineStr"/>
       <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -6068,12 +5646,9 @@
           <t>241</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H144" s="2" t="inlineStr"/>
       <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -6107,12 +5682,9 @@
           <t>170</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H145" s="2" t="inlineStr"/>
       <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -6146,12 +5718,9 @@
           <t>446,25</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H146" s="2" t="inlineStr"/>
       <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -6185,12 +5754,9 @@
           <t>711,66</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H147" s="2" t="inlineStr"/>
       <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -6224,12 +5790,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H148" s="2" t="inlineStr"/>
       <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -6263,12 +5826,9 @@
           <t>107,24</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H149" s="2" t="inlineStr"/>
       <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -6302,12 +5862,9 @@
           <t>365,49</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H150" s="2" t="inlineStr"/>
       <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -6341,12 +5898,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H151" s="2" t="inlineStr"/>
       <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -6380,12 +5934,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H152" s="2" t="inlineStr"/>
       <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -6419,12 +5970,9 @@
           <t>209,56</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H153" s="2" t="inlineStr"/>
       <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -6458,12 +6006,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H154" s="2" t="inlineStr"/>
       <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -6497,12 +6042,9 @@
           <t>12,03</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H155" s="2" t="inlineStr"/>
       <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -6536,12 +6078,9 @@
           <t>84,82</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H156" s="2" t="inlineStr"/>
       <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -6575,12 +6114,9 @@
           <t>545</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H157" s="2" t="inlineStr"/>
       <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -6614,12 +6150,9 @@
           <t>116</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H158" s="2" t="inlineStr"/>
       <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -6653,12 +6186,9 @@
           <t>152</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H159" s="2" t="inlineStr"/>
       <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -6692,12 +6222,9 @@
           <t>15</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H160" s="2" t="inlineStr"/>
       <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -6731,12 +6258,9 @@
           <t>891,48</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H161" s="2" t="inlineStr"/>
       <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -6770,12 +6294,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H162" s="2" t="inlineStr"/>
       <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -6809,12 +6330,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H163" s="2" t="inlineStr"/>
       <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -6848,12 +6366,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H164" s="2" t="inlineStr"/>
       <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -6887,12 +6402,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H165" s="2" t="inlineStr"/>
       <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -6926,12 +6438,9 @@
           <t>9.846</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H166" s="2" t="inlineStr"/>
       <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -6965,12 +6474,9 @@
           <t>48</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H167" s="2" t="inlineStr"/>
       <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -7004,12 +6510,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H168" s="2" t="inlineStr"/>
       <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -7043,12 +6546,9 @@
           <t>86,83</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H169" s="2" t="inlineStr"/>
       <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -7082,12 +6582,9 @@
           <t>622,80</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H170" s="2" t="inlineStr"/>
       <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -7121,12 +6618,9 @@
           <t>483,83</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H171" s="2" t="inlineStr"/>
       <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -7160,12 +6654,9 @@
           <t>148</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H172" s="2" t="inlineStr"/>
       <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -7199,12 +6690,9 @@
           <t>1.374,60</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H173" s="2" t="inlineStr"/>
       <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -7238,12 +6726,9 @@
           <t>11</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H174" s="2" t="inlineStr"/>
       <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -7277,12 +6762,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H175" s="2" t="inlineStr"/>
       <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -7316,12 +6798,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H176" s="2" t="inlineStr"/>
       <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -7355,12 +6834,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H177" s="2" t="inlineStr"/>
       <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -7394,12 +6870,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H178" s="2" t="inlineStr"/>
       <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -7433,12 +6906,9 @@
           <t>162</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H179" s="2" t="inlineStr"/>
       <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -7472,12 +6942,9 @@
           <t>230</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H180" s="2" t="inlineStr"/>
       <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -7511,12 +6978,9 @@
           <t>227</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H181" s="2" t="inlineStr"/>
       <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -7550,12 +7014,9 @@
           <t>748</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H182" s="2" t="inlineStr"/>
       <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -7589,12 +7050,9 @@
           <t>4.598,75</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H183" s="2" t="inlineStr"/>
       <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -7628,12 +7086,9 @@
           <t>280</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H184" s="2" t="inlineStr"/>
       <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -7667,12 +7122,9 @@
           <t>2.535,34</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H185" s="2" t="inlineStr"/>
       <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -7706,12 +7158,9 @@
           <t>924,23</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H186" s="2" t="inlineStr"/>
       <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -7745,12 +7194,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H187" s="2" t="inlineStr"/>
       <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -7784,12 +7230,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H188" s="2" t="inlineStr"/>
       <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -7823,12 +7266,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H189" s="2" t="inlineStr"/>
       <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -7862,12 +7302,9 @@
           <t>14,43</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H190" s="2" t="inlineStr"/>
       <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -7901,12 +7338,9 @@
           <t>24,44</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H191" s="2" t="inlineStr"/>
       <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -7940,12 +7374,9 @@
           <t>148</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H192" s="2" t="inlineStr"/>
       <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -7979,12 +7410,9 @@
           <t>157</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H193" s="2" t="inlineStr"/>
       <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -8018,12 +7446,9 @@
           <t>111</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H194" s="2" t="inlineStr"/>
       <c r="I194" s="2" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -8057,12 +7482,9 @@
           <t>358,80</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H195" s="2" t="inlineStr"/>
       <c r="I195" s="2" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -8096,12 +7518,9 @@
           <t>22</t>
         </is>
       </c>
-      <c r="H196" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H196" s="2" t="inlineStr"/>
       <c r="I196" s="2" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -8135,12 +7554,9 @@
           <t>14</t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H197" s="2" t="inlineStr"/>
       <c r="I197" s="2" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -8174,12 +7590,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H198" s="2" t="inlineStr"/>
       <c r="I198" s="2" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -8213,12 +7626,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H199" s="2" t="inlineStr"/>
       <c r="I199" s="2" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -8252,12 +7662,9 @@
           <t>354,17</t>
         </is>
       </c>
-      <c r="H200" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H200" s="2" t="inlineStr"/>
       <c r="I200" s="2" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -8291,12 +7698,9 @@
           <t>3.662</t>
         </is>
       </c>
-      <c r="H201" s="2" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="H201" s="2" t="inlineStr"/>
       <c r="I201" s="2" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -8317,7 +7721,7 @@
   <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" style="4" min="1" max="1"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8327,45 +7731,49 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr"/>
+    </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>1. Aprire il PDF della provincia alla 'pagina PDF' indicata (numero di pagina del file, non quello stampato).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2. Trovare il blocco 'REGIONE AGRARIA n' (colonna 'id': TO1 = regione agraria 1) e la riga della 'classe'.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>3. Guardare solo le colonne TOTALE (Aziende o Superficie, come indicato).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>4. Confrontare con 'valore trascritto': scrivere si se identico, no se diverso.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>5. Se no, scrivere nella colonna successiva il valore come stampato (es. 1.451,79 oppure —).</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr"/>
+    </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Il trattino — significa zero/nessuna azienda.</t>
         </is>

--- a/output/audit_torino.xlsx
+++ b/output/audit_torino.xlsx
@@ -535,9 +535,17 @@
           <t>541,92</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>controllo: OCR e lettura visiva concordi</t>
@@ -576,9 +584,17 @@
           <t>2.332,91</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -617,9 +633,17 @@
           <t>1.273,26</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -658,9 +682,17 @@
           <t>32,18</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>controllo: OCR e lettura visiva concordi</t>
@@ -699,9 +731,17 @@
           <t>643,97</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>riletta su zoom / ricostruita da somma di riga</t>
@@ -740,9 +780,17 @@
           <t>417,01</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>controllo: OCR e lettura visiva concordi</t>
@@ -781,9 +829,17 @@
           <t>1.821,71</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -822,9 +878,17 @@
           <t>1.080</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -863,9 +927,17 @@
           <t>1.351,32</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -904,9 +976,17 @@
           <t>1.737,32</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -945,9 +1025,17 @@
           <t>1.065</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -986,9 +1074,17 @@
           <t>18</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>controllo: OCR e lettura visiva concordi</t>
@@ -1027,9 +1123,17 @@
           <t>1.070,20</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1068,9 +1172,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>controllo: OCR e lettura visiva concordi</t>
@@ -1109,9 +1221,17 @@
           <t>1.604,47</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1150,9 +1270,17 @@
           <t>1.150,57</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1191,9 +1319,17 @@
           <t>1.195,53</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1232,9 +1368,17 @@
           <t>226</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>controllo: OCR e lettura visiva concordi</t>
@@ -1273,9 +1417,17 @@
           <t>251</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>controllo: OCR e lettura visiva concordi</t>
@@ -1314,9 +1466,17 @@
           <t>1.349,96</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1355,9 +1515,17 @@
           <t>5.495,88</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1396,9 +1564,17 @@
           <t>9,51</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1437,9 +1613,17 @@
           <t>10</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>controllo: OCR e lettura visiva concordi</t>
@@ -1478,9 +1662,17 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1519,9 +1711,17 @@
           <t>5.152</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1560,9 +1760,17 @@
           <t>1.474,06</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1601,9 +1809,17 @@
           <t>1.073,25</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1642,9 +1858,17 @@
           <t>2.715,12</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1683,9 +1907,17 @@
           <t>924,23</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1724,9 +1956,17 @@
           <t>79,17</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1765,9 +2005,17 @@
           <t>176,15</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1806,9 +2054,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1847,9 +2103,17 @@
           <t>2.666,67</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1888,9 +2152,17 @@
           <t>2.080,55</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1926,9 +2198,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1964,9 +2234,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -2002,9 +2270,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
